--- a/VerveStacks_IND_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BB31F0-E5AF-4D3B-8BD9-4BF14654CEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CB2A67-BBAA-4B6E-B02F-B988DC8781E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6230,7 +6230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C077FAD0-ADE4-4D2D-9551-F5C4465CCC91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01704608-6B8F-45B8-BEEF-BBE145FF8774}">
   <dimension ref="B3:I352"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CB2A67-BBAA-4B6E-B02F-B988DC8781E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B61F95-B675-4202-B090-DC54AC9D62DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6230,7 +6230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01704608-6B8F-45B8-BEEF-BBE145FF8774}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5DCEB0-0873-485F-9841-5A948A44EB5D}">
   <dimension ref="B3:I352"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B61F95-B675-4202-B090-DC54AC9D62DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2127DE9D-0702-4E38-A9CE-63505F1658BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6230,7 +6230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5DCEB0-0873-485F-9841-5A948A44EB5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DB6CC1-57F3-4460-8687-28A700AAECFE}">
   <dimension ref="B3:I352"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2127DE9D-0702-4E38-A9CE-63505F1658BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613A71C1-42BD-408B-B998-2C9F829E7961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4537" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4564" uniqueCount="1270">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -3816,6 +3816,39 @@
   </si>
   <si>
     <t>grid node -- way/97392607-765</t>
+  </si>
+  <si>
+    <t>ctype</t>
+  </si>
+  <si>
+    <t>ELC4H</t>
+  </si>
+  <si>
+    <t>First 5 hours of surplus electricity from VRE generation</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>ELC8H</t>
+  </si>
+  <si>
+    <t>6-10 hours of surplus electricity from VRE generation</t>
+  </si>
+  <si>
+    <t>DEF_E</t>
+  </si>
+  <si>
+    <t>Electricity that was missing at the hourly level</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
+  </si>
+  <si>
+    <t>VRE Capacity deficit to be covered by dispatchable techs</t>
+  </si>
+  <si>
+    <t>GW</t>
   </si>
 </sst>
 </file>
@@ -16288,7 +16321,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="13:19">
+    <row r="33" spans="2:19">
       <c r="M33" t="s">
         <v>17</v>
       </c>
@@ -16311,7 +16344,10 @@
         <v>224</v>
       </c>
     </row>
-    <row r="34" spans="13:19">
+    <row r="34" spans="2:19">
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
       <c r="M34" t="s">
         <v>17</v>
       </c>
@@ -16334,7 +16370,25 @@
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="13:19">
+    <row r="35" spans="2:19">
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1259</v>
+      </c>
       <c r="M35" t="s">
         <v>17</v>
       </c>
@@ -16357,7 +16411,25 @@
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="13:19">
+    <row r="36" spans="2:19">
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
+      </c>
       <c r="M36" t="s">
         <v>17</v>
       </c>
@@ -16380,7 +16452,22 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="13:19">
+    <row r="37" spans="2:19">
+      <c r="C37" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G37" t="s">
+        <v>25</v>
+      </c>
       <c r="M37" t="s">
         <v>17</v>
       </c>
@@ -16403,7 +16490,22 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="13:19">
+    <row r="38" spans="2:19">
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1262</v>
+      </c>
       <c r="M38" t="s">
         <v>17</v>
       </c>
@@ -16426,7 +16528,19 @@
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="13:19">
+    <row r="39" spans="2:19">
+      <c r="C39" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F39" t="s">
+        <v>186</v>
+      </c>
       <c r="M39" t="s">
         <v>17</v>
       </c>
@@ -16449,7 +16563,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="13:19">
+    <row r="40" spans="2:19">
       <c r="M40" t="s">
         <v>17</v>
       </c>
@@ -16472,7 +16586,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="41" spans="13:19">
+    <row r="41" spans="2:19">
       <c r="M41" t="s">
         <v>17</v>
       </c>
@@ -16495,7 +16609,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="42" spans="13:19">
+    <row r="42" spans="2:19">
       <c r="M42" t="s">
         <v>17</v>
       </c>
@@ -16518,7 +16632,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="43" spans="13:19">
+    <row r="43" spans="2:19">
       <c r="M43" t="s">
         <v>17</v>
       </c>
@@ -16541,7 +16655,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="44" spans="13:19">
+    <row r="44" spans="2:19">
       <c r="M44" t="s">
         <v>17</v>
       </c>
@@ -16564,7 +16678,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="13:19">
+    <row r="45" spans="2:19">
       <c r="M45" t="s">
         <v>17</v>
       </c>
@@ -16587,7 +16701,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="13:19">
+    <row r="46" spans="2:19">
       <c r="M46" t="s">
         <v>17</v>
       </c>
@@ -16610,7 +16724,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="13:19">
+    <row r="47" spans="2:19">
       <c r="M47" t="s">
         <v>17</v>
       </c>
@@ -16633,7 +16747,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="13:19">
+    <row r="48" spans="2:19">
       <c r="M48" t="s">
         <v>17</v>
       </c>
